--- a/artfynd/A 29803-2023 artfynd.xlsx
+++ b/artfynd/A 29803-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29803-2023 artfynd.xlsx
+++ b/artfynd/A 29803-2023 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>111863045</v>
       </c>
       <c r="B2" t="n">
-        <v>89033</v>
+        <v>90043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -721,14 +721,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>655234</v>
       </c>
       <c r="R2" t="n">
-        <v>6634889</v>
+        <v>6634890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>

--- a/artfynd/A 29803-2023 artfynd.xlsx
+++ b/artfynd/A 29803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>111863045</v>
       </c>
       <c r="B2" t="n">
-        <v>90043</v>
+        <v>90060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29803-2023 artfynd.xlsx
+++ b/artfynd/A 29803-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111863045</v>
       </c>
       <c r="B2" t="n">
-        <v>90060</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,12 +800,7 @@
         <v>111863073</v>
       </c>
       <c r="B3" t="n">
-        <v>89033</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,7 +838,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -924,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111862959</v>
+        <v>111863001</v>
       </c>
       <c r="B4" t="n">
-        <v>90821</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,26 +925,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,7 +959,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655218</v>
+        <v>655217</v>
       </c>
       <c r="R4" t="n">
         <v>6634940</v>
@@ -1009,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Under gran och tall i en svacka</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111863001</v>
+        <v>111863745</v>
       </c>
       <c r="B5" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,12 +1056,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,14 +1072,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Charlottenberg, Upl</t>
+          <t>Linnés Hammarby kulturreservat, Linnés Hammarby kulturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655218</v>
+        <v>655222</v>
       </c>
       <c r="R5" t="n">
-        <v>6634940</v>
+        <v>6634686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,15 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111863269</v>
+        <v>111862959</v>
       </c>
       <c r="B6" t="n">
-        <v>85183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,26 +1159,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1219,14 +1189,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Charlottenberg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655135</v>
+        <v>655217</v>
       </c>
       <c r="R6" t="n">
-        <v>6634800</v>
+        <v>6634940</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 ex i gräsglänta under gran och tall.</t>
+          <t>Under gran och tall i en svacka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,60 +1270,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111863218</v>
+        <v>111863040</v>
       </c>
       <c r="B7" t="n">
-        <v>90155</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655138</v>
+        <v>655235</v>
       </c>
       <c r="R7" t="n">
-        <v>6634821</v>
+        <v>6634878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1395,7 +1351,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Halv häxring, 3 m i diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,15 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111863288</v>
+        <v>111863402</v>
       </c>
       <c r="B8" t="n">
-        <v>85183</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,21 +1394,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1468,14 +1424,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655135</v>
+        <v>655200</v>
       </c>
       <c r="R8" t="n">
-        <v>6634793</v>
+        <v>6634770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,19 +1500,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111863040</v>
+        <v>111863416</v>
       </c>
       <c r="B9" t="n">
-        <v>90821</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1569,26 +1520,35 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655235</v>
+        <v>655221</v>
       </c>
       <c r="R9" t="n">
-        <v>6634878</v>
+        <v>6634779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1630,12 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Halv häxring, 3 m i diameter</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,19 +1617,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111863402</v>
+        <v>111863754</v>
       </c>
       <c r="B10" t="n">
-        <v>90821</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1687,35 +1637,26 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Charlottenberg (Charlottenberg), Upl</t>
+          <t>Linnés Hammarby kulturreservat, Linnés Hammarby kulturreservat, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655200</v>
+        <v>655222</v>
       </c>
       <c r="R10" t="n">
-        <v>6634770</v>
+        <v>6634686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,6 +1701,11 @@
           <t>11:02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stor häxring</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1781,6 +1727,362 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111863218</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>655138</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6634821</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111863269</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>655135</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6634800</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 ex i gräsglänta under gran och tall.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111863288</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Charlottenberg, Charlottenberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>655134</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6634793</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
